--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120276067</v>
+        <v>120276081</v>
       </c>
       <c r="B2" t="n">
-        <v>57326</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>778026</v>
+        <v>778112</v>
       </c>
       <c r="R2" t="n">
-        <v>7299789</v>
+        <v>7299748</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120276082</v>
+        <v>120276067</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778126</v>
+        <v>778026</v>
       </c>
       <c r="R3" t="n">
-        <v>7299758</v>
+        <v>7299789</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120276077</v>
+        <v>120276082</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778024</v>
+        <v>778126</v>
       </c>
       <c r="R4" t="n">
-        <v>7299781</v>
+        <v>7299758</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>120276078</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120276081</v>
+        <v>120276077</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778112</v>
+        <v>778024</v>
       </c>
       <c r="R6" t="n">
-        <v>7299748</v>
+        <v>7299781</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120276081</v>
+        <v>120276078</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>778112</v>
+        <v>778023</v>
       </c>
       <c r="R2" t="n">
-        <v>7299748</v>
+        <v>7299762</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120276067</v>
+        <v>120276081</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778026</v>
+        <v>778112</v>
       </c>
       <c r="R3" t="n">
-        <v>7299789</v>
+        <v>7299748</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120276082</v>
+        <v>120276077</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778126</v>
+        <v>778024</v>
       </c>
       <c r="R4" t="n">
-        <v>7299758</v>
+        <v>7299781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120276078</v>
+        <v>120276067</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778023</v>
+        <v>778026</v>
       </c>
       <c r="R5" t="n">
-        <v>7299762</v>
+        <v>7299789</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120276077</v>
+        <v>120276082</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778024</v>
+        <v>778126</v>
       </c>
       <c r="R6" t="n">
-        <v>7299781</v>
+        <v>7299758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120276078</v>
+        <v>120276081</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>778023</v>
+        <v>778112</v>
       </c>
       <c r="R2" t="n">
-        <v>7299762</v>
+        <v>7299748</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120276081</v>
+        <v>120276082</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778112</v>
+        <v>778126</v>
       </c>
       <c r="R3" t="n">
-        <v>7299748</v>
+        <v>7299758</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120276082</v>
+        <v>120276078</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778126</v>
+        <v>778023</v>
       </c>
       <c r="R6" t="n">
-        <v>7299758</v>
+        <v>7299762</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,6 +1182,415 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120447938</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78624</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>864</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>777894</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7299834</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120447939</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>777918</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7299801</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120447944</v>
+      </c>
+      <c r="B9" t="n">
+        <v>82321</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>777914</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7299812</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120447910</v>
+      </c>
+      <c r="B10" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>777954</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7299815</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120276081</v>
+        <v>120276067</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>778112</v>
+        <v>778026</v>
       </c>
       <c r="R2" t="n">
-        <v>7299748</v>
+        <v>7299789</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120276067</v>
+        <v>120276081</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778026</v>
+        <v>778112</v>
       </c>
       <c r="R5" t="n">
-        <v>7299789</v>
+        <v>7299748</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120447938</v>
+        <v>120447910</v>
       </c>
       <c r="B7" t="n">
-        <v>78624</v>
+        <v>74654</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777894</v>
+        <v>777954</v>
       </c>
       <c r="R7" t="n">
-        <v>7299834</v>
+        <v>7299815</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,7 +1269,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1492,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120447910</v>
+        <v>120447938</v>
       </c>
       <c r="B10" t="n">
-        <v>74654</v>
+        <v>78624</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1532,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777954</v>
+        <v>777894</v>
       </c>
       <c r="R10" t="n">
-        <v>7299815</v>
+        <v>7299834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,6 +1575,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120276067</v>
+        <v>120276077</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>778026</v>
+        <v>778024</v>
       </c>
       <c r="R2" t="n">
-        <v>7299789</v>
+        <v>7299781</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120276082</v>
+        <v>120276067</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778126</v>
+        <v>778026</v>
       </c>
       <c r="R3" t="n">
-        <v>7299758</v>
+        <v>7299789</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120276077</v>
+        <v>120276081</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778024</v>
+        <v>778112</v>
       </c>
       <c r="R4" t="n">
-        <v>7299781</v>
+        <v>7299748</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120276081</v>
+        <v>120276078</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778112</v>
+        <v>778023</v>
       </c>
       <c r="R5" t="n">
-        <v>7299748</v>
+        <v>7299762</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120276078</v>
+        <v>120276082</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778023</v>
+        <v>778126</v>
       </c>
       <c r="R6" t="n">
-        <v>7299762</v>
+        <v>7299758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120447910</v>
+        <v>120447939</v>
       </c>
       <c r="B7" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777954</v>
+        <v>777918</v>
       </c>
       <c r="R7" t="n">
-        <v>7299815</v>
+        <v>7299801</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120447939</v>
+        <v>120447938</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>78624</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777918</v>
+        <v>777894</v>
       </c>
       <c r="R8" t="n">
-        <v>7299801</v>
+        <v>7299834</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,6 +1371,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1389,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120447944</v>
+        <v>120447910</v>
       </c>
       <c r="B9" t="n">
-        <v>82321</v>
+        <v>74654</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1406,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777914</v>
+        <v>777954</v>
       </c>
       <c r="R9" t="n">
-        <v>7299812</v>
+        <v>7299815</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1492,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120447938</v>
+        <v>120447944</v>
       </c>
       <c r="B10" t="n">
-        <v>78624</v>
+        <v>82321</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1508,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777894</v>
+        <v>777914</v>
       </c>
       <c r="R10" t="n">
-        <v>7299834</v>
+        <v>7299812</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1576,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120276077</v>
+        <v>120276078</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>778024</v>
+        <v>778023</v>
       </c>
       <c r="R2" t="n">
-        <v>7299781</v>
+        <v>7299762</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120276081</v>
+        <v>120276082</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778112</v>
+        <v>778126</v>
       </c>
       <c r="R4" t="n">
-        <v>7299748</v>
+        <v>7299758</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120276078</v>
+        <v>120276077</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778023</v>
+        <v>778024</v>
       </c>
       <c r="R5" t="n">
-        <v>7299762</v>
+        <v>7299781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120276082</v>
+        <v>120276081</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778126</v>
+        <v>778112</v>
       </c>
       <c r="R6" t="n">
-        <v>7299758</v>
+        <v>7299748</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120447939</v>
+        <v>120447938</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>78624</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777918</v>
+        <v>777894</v>
       </c>
       <c r="R7" t="n">
-        <v>7299801</v>
+        <v>7299834</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,6 +1269,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,10 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120447938</v>
+        <v>120447910</v>
       </c>
       <c r="B8" t="n">
-        <v>78624</v>
+        <v>74654</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1304,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777894</v>
+        <v>777954</v>
       </c>
       <c r="R8" t="n">
-        <v>7299834</v>
+        <v>7299815</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,7 +1372,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120447910</v>
+        <v>120447944</v>
       </c>
       <c r="B9" t="n">
-        <v>74654</v>
+        <v>82321</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,21 +1406,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777954</v>
+        <v>777914</v>
       </c>
       <c r="R9" t="n">
-        <v>7299815</v>
+        <v>7299812</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,10 +1492,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120447944</v>
+        <v>120447939</v>
       </c>
       <c r="B10" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,21 +1508,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777914</v>
+        <v>777918</v>
       </c>
       <c r="R10" t="n">
-        <v>7299812</v>
+        <v>7299801</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120276078</v>
+        <v>120276067</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>778023</v>
+        <v>778026</v>
       </c>
       <c r="R2" t="n">
-        <v>7299762</v>
+        <v>7299789</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120276067</v>
+        <v>120276077</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778026</v>
+        <v>778024</v>
       </c>
       <c r="R3" t="n">
-        <v>7299789</v>
+        <v>7299781</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120276082</v>
+        <v>120276081</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778126</v>
+        <v>778112</v>
       </c>
       <c r="R4" t="n">
-        <v>7299758</v>
+        <v>7299748</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120276077</v>
+        <v>120276078</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778024</v>
+        <v>778023</v>
       </c>
       <c r="R5" t="n">
-        <v>7299781</v>
+        <v>7299762</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120276081</v>
+        <v>120276082</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778112</v>
+        <v>778126</v>
       </c>
       <c r="R6" t="n">
-        <v>7299748</v>
+        <v>7299758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120447938</v>
+        <v>120447944</v>
       </c>
       <c r="B7" t="n">
-        <v>78624</v>
+        <v>82321</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777894</v>
+        <v>777914</v>
       </c>
       <c r="R7" t="n">
-        <v>7299834</v>
+        <v>7299812</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,7 +1269,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1288,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120447910</v>
+        <v>120447938</v>
       </c>
       <c r="B8" t="n">
-        <v>74654</v>
+        <v>78624</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1328,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777954</v>
+        <v>777894</v>
       </c>
       <c r="R8" t="n">
-        <v>7299815</v>
+        <v>7299834</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,6 +1371,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120447944</v>
+        <v>120447910</v>
       </c>
       <c r="B9" t="n">
-        <v>82321</v>
+        <v>74654</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,21 +1406,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777914</v>
+        <v>777954</v>
       </c>
       <c r="R9" t="n">
-        <v>7299812</v>
+        <v>7299815</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1592,6 +1592,210 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122857762</v>
+      </c>
+      <c r="B11" t="n">
+        <v>94380</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2387</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Källpraktmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pseudobryum cinclidioides</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>778016</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7299730</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122857765</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>778128</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7299758</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122857762</v>
+        <v>122857765</v>
       </c>
       <c r="B11" t="n">
-        <v>94380</v>
+        <v>98357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1606,25 +1606,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>778016</v>
+        <v>778128</v>
       </c>
       <c r="R11" t="n">
-        <v>7299730</v>
+        <v>7299758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122857765</v>
+        <v>122857762</v>
       </c>
       <c r="B12" t="n">
-        <v>98355</v>
+        <v>94382</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1708,25 +1708,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>778128</v>
+        <v>778016</v>
       </c>
       <c r="R12" t="n">
-        <v>7299758</v>
+        <v>7299730</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122857765</v>
+        <v>122857762</v>
       </c>
       <c r="B11" t="n">
-        <v>98357</v>
+        <v>94382</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1606,25 +1606,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>778128</v>
+        <v>778016</v>
       </c>
       <c r="R11" t="n">
-        <v>7299758</v>
+        <v>7299730</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122857762</v>
+        <v>122857765</v>
       </c>
       <c r="B12" t="n">
-        <v>94382</v>
+        <v>98357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1708,25 +1708,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>778016</v>
+        <v>778128</v>
       </c>
       <c r="R12" t="n">
-        <v>7299730</v>
+        <v>7299758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122857762</v>
+        <v>122857765</v>
       </c>
       <c r="B11" t="n">
-        <v>94382</v>
+        <v>98365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1606,25 +1606,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>778016</v>
+        <v>778128</v>
       </c>
       <c r="R11" t="n">
-        <v>7299730</v>
+        <v>7299758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122857765</v>
+        <v>122857762</v>
       </c>
       <c r="B12" t="n">
-        <v>98357</v>
+        <v>94390</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1708,25 +1708,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>778128</v>
+        <v>778016</v>
       </c>
       <c r="R12" t="n">
-        <v>7299758</v>
+        <v>7299730</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1796,6 +1796,320 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123338979</v>
+      </c>
+      <c r="B13" t="n">
+        <v>82553</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>777970</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7299864</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123338980</v>
+      </c>
+      <c r="B14" t="n">
+        <v>82553</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>778008</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7299929</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123338983</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57398</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102110</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fjällvråk</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Buteo lagopus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>777999</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7299812</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122857765</v>
+        <v>122857762</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>94393</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1606,25 +1606,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>778128</v>
+        <v>778016</v>
       </c>
       <c r="R11" t="n">
-        <v>7299758</v>
+        <v>7299730</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122857762</v>
+        <v>122857765</v>
       </c>
       <c r="B12" t="n">
-        <v>94390</v>
+        <v>98368</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1708,25 +1708,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>778016</v>
+        <v>778128</v>
       </c>
       <c r="R12" t="n">
-        <v>7299730</v>
+        <v>7299758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123338979</v>
+        <v>123338983</v>
       </c>
       <c r="B13" t="n">
-        <v>82553</v>
+        <v>57401</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,34 +1814,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>102110</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777970</v>
+        <v>777999</v>
       </c>
       <c r="R13" t="n">
-        <v>7299864</v>
+        <v>7299812</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,7 +1901,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1903,7 +1911,7 @@
         <v>123338980</v>
       </c>
       <c r="B14" t="n">
-        <v>82553</v>
+        <v>82556</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2002,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123338983</v>
+        <v>123338979</v>
       </c>
       <c r="B15" t="n">
-        <v>57398</v>
+        <v>82556</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,42 +2026,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102110</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777999</v>
+        <v>777970</v>
       </c>
       <c r="R15" t="n">
-        <v>7299812</v>
+        <v>7299864</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,10 +2105,418 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123421320</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78769</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>778005</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7299869</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123421319</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>777992</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7299708</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123421323</v>
+      </c>
+      <c r="B18" t="n">
+        <v>82556</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>778048</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7299925</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123421322</v>
+      </c>
+      <c r="B19" t="n">
+        <v>82556</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>778035</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7299897</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1597,7 +1597,7 @@
         <v>122857762</v>
       </c>
       <c r="B11" t="n">
-        <v>94393</v>
+        <v>94395</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>122857765</v>
       </c>
       <c r="B12" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123338980</v>
+        <v>123338979</v>
       </c>
       <c r="B14" t="n">
-        <v>82556</v>
+        <v>82558</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>778008</v>
+        <v>777970</v>
       </c>
       <c r="R14" t="n">
-        <v>7299929</v>
+        <v>7299864</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123338979</v>
+        <v>123338980</v>
       </c>
       <c r="B15" t="n">
-        <v>82556</v>
+        <v>82558</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777970</v>
+        <v>778008</v>
       </c>
       <c r="R15" t="n">
-        <v>7299864</v>
+        <v>7299929</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123421320</v>
+        <v>123421323</v>
       </c>
       <c r="B16" t="n">
-        <v>78769</v>
+        <v>82558</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>778005</v>
+        <v>778048</v>
       </c>
       <c r="R16" t="n">
-        <v>7299869</v>
+        <v>7299925</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123421319</v>
+        <v>123421320</v>
       </c>
       <c r="B17" t="n">
-        <v>57497</v>
+        <v>78771</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777992</v>
+        <v>778005</v>
       </c>
       <c r="R17" t="n">
-        <v>7299708</v>
+        <v>7299869</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123421323</v>
+        <v>123421322</v>
       </c>
       <c r="B18" t="n">
-        <v>82556</v>
+        <v>82558</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>778048</v>
+        <v>778035</v>
       </c>
       <c r="R18" t="n">
-        <v>7299925</v>
+        <v>7299897</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123421322</v>
+        <v>123421319</v>
       </c>
       <c r="B19" t="n">
-        <v>82556</v>
+        <v>57497</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>778035</v>
+        <v>777992</v>
       </c>
       <c r="R19" t="n">
-        <v>7299897</v>
+        <v>7299708</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122857762</v>
+        <v>122857765</v>
       </c>
       <c r="B11" t="n">
-        <v>94395</v>
+        <v>98376</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1606,25 +1606,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>778016</v>
+        <v>778128</v>
       </c>
       <c r="R11" t="n">
-        <v>7299730</v>
+        <v>7299758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122857765</v>
+        <v>122857762</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>94401</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1708,25 +1708,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>778128</v>
+        <v>778016</v>
       </c>
       <c r="R12" t="n">
-        <v>7299758</v>
+        <v>7299730</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123338983</v>
+        <v>123338979</v>
       </c>
       <c r="B13" t="n">
-        <v>57401</v>
+        <v>82559</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,42 +1814,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102110</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777999</v>
+        <v>777970</v>
       </c>
       <c r="R13" t="n">
-        <v>7299812</v>
+        <v>7299864</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,17 +1893,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123338979</v>
+        <v>123338980</v>
       </c>
       <c r="B14" t="n">
-        <v>82558</v>
+        <v>82559</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1948,10 +1940,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777970</v>
+        <v>778008</v>
       </c>
       <c r="R14" t="n">
-        <v>7299864</v>
+        <v>7299929</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,10 +2002,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123338980</v>
+        <v>123338983</v>
       </c>
       <c r="B15" t="n">
-        <v>82558</v>
+        <v>57401</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,34 +2018,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>102110</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>778008</v>
+        <v>777999</v>
       </c>
       <c r="R15" t="n">
-        <v>7299929</v>
+        <v>7299812</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2115,7 +2115,7 @@
         <v>123421323</v>
       </c>
       <c r="B16" t="n">
-        <v>82558</v>
+        <v>82559</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123421320</v>
+        <v>123421319</v>
       </c>
       <c r="B17" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>778005</v>
+        <v>777992</v>
       </c>
       <c r="R17" t="n">
-        <v>7299869</v>
+        <v>7299708</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123421322</v>
+        <v>123421320</v>
       </c>
       <c r="B18" t="n">
-        <v>82558</v>
+        <v>78772</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>778035</v>
+        <v>778005</v>
       </c>
       <c r="R18" t="n">
-        <v>7299897</v>
+        <v>7299869</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123421319</v>
+        <v>123421322</v>
       </c>
       <c r="B19" t="n">
-        <v>57497</v>
+        <v>82559</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777992</v>
+        <v>778035</v>
       </c>
       <c r="R19" t="n">
-        <v>7299708</v>
+        <v>7299897</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1798,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123338983</v>
+        <v>123338979</v>
       </c>
       <c r="B13" t="n">
-        <v>57401</v>
+        <v>82568</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,42 +1814,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102110</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777999</v>
+        <v>777970</v>
       </c>
       <c r="R13" t="n">
-        <v>7299812</v>
+        <v>7299864</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,7 +1893,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1911,7 +1903,7 @@
         <v>123338980</v>
       </c>
       <c r="B14" t="n">
-        <v>82562</v>
+        <v>82568</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2010,10 +2002,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123338979</v>
+        <v>123338983</v>
       </c>
       <c r="B15" t="n">
-        <v>82562</v>
+        <v>57407</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,34 +2018,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>102110</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777970</v>
+        <v>777999</v>
       </c>
       <c r="R15" t="n">
-        <v>7299864</v>
+        <v>7299812</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,17 +2105,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123421322</v>
+        <v>123421323</v>
       </c>
       <c r="B16" t="n">
-        <v>82562</v>
+        <v>82568</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>778035</v>
+        <v>778048</v>
       </c>
       <c r="R16" t="n">
-        <v>7299897</v>
+        <v>7299925</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123421323</v>
+        <v>123421319</v>
       </c>
       <c r="B17" t="n">
-        <v>82562</v>
+        <v>57503</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>778048</v>
+        <v>777992</v>
       </c>
       <c r="R17" t="n">
-        <v>7299925</v>
+        <v>7299708</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2319,7 +2319,7 @@
         <v>123421320</v>
       </c>
       <c r="B18" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123421319</v>
+        <v>123421322</v>
       </c>
       <c r="B19" t="n">
-        <v>57497</v>
+        <v>82568</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777992</v>
+        <v>778035</v>
       </c>
       <c r="R19" t="n">
-        <v>7299708</v>
+        <v>7299897</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1798,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123338979</v>
+        <v>123338980</v>
       </c>
       <c r="B13" t="n">
-        <v>82568</v>
+        <v>82573</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777970</v>
+        <v>778008</v>
       </c>
       <c r="R13" t="n">
-        <v>7299864</v>
+        <v>7299929</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123338980</v>
+        <v>123338979</v>
       </c>
       <c r="B14" t="n">
-        <v>82568</v>
+        <v>82573</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>778008</v>
+        <v>777970</v>
       </c>
       <c r="R14" t="n">
-        <v>7299929</v>
+        <v>7299864</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,7 +2005,7 @@
         <v>123338983</v>
       </c>
       <c r="B15" t="n">
-        <v>57407</v>
+        <v>57410</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123421323</v>
+        <v>123421319</v>
       </c>
       <c r="B16" t="n">
-        <v>82568</v>
+        <v>57506</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>778048</v>
+        <v>777992</v>
       </c>
       <c r="R16" t="n">
-        <v>7299925</v>
+        <v>7299708</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123421319</v>
+        <v>123421322</v>
       </c>
       <c r="B17" t="n">
-        <v>57503</v>
+        <v>82573</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777992</v>
+        <v>778035</v>
       </c>
       <c r="R17" t="n">
-        <v>7299708</v>
+        <v>7299897</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123421320</v>
+        <v>123421323</v>
       </c>
       <c r="B18" t="n">
-        <v>78781</v>
+        <v>82573</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>778005</v>
+        <v>778048</v>
       </c>
       <c r="R18" t="n">
-        <v>7299869</v>
+        <v>7299925</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123421322</v>
+        <v>123421320</v>
       </c>
       <c r="B19" t="n">
-        <v>82568</v>
+        <v>78786</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>778035</v>
+        <v>778005</v>
       </c>
       <c r="R19" t="n">
-        <v>7299897</v>
+        <v>7299869</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1801,7 +1801,7 @@
         <v>123338980</v>
       </c>
       <c r="B13" t="n">
-        <v>82573</v>
+        <v>82575</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>123338979</v>
       </c>
       <c r="B14" t="n">
-        <v>82573</v>
+        <v>82575</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>123338983</v>
       </c>
       <c r="B15" t="n">
-        <v>57410</v>
+        <v>57411</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>123421319</v>
       </c>
       <c r="B16" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123421322</v>
+        <v>123421320</v>
       </c>
       <c r="B17" t="n">
-        <v>82573</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>778035</v>
+        <v>778005</v>
       </c>
       <c r="R17" t="n">
-        <v>7299897</v>
+        <v>7299869</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2319,7 +2319,7 @@
         <v>123421323</v>
       </c>
       <c r="B18" t="n">
-        <v>82573</v>
+        <v>82575</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123421320</v>
+        <v>123421322</v>
       </c>
       <c r="B19" t="n">
-        <v>78786</v>
+        <v>82575</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>778005</v>
+        <v>778035</v>
       </c>
       <c r="R19" t="n">
-        <v>7299869</v>
+        <v>7299897</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1798,7 +1798,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123338980</v>
+        <v>123338979</v>
       </c>
       <c r="B13" t="n">
         <v>82575</v>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>778008</v>
+        <v>777970</v>
       </c>
       <c r="R13" t="n">
-        <v>7299929</v>
+        <v>7299864</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123338979</v>
+        <v>123338980</v>
       </c>
       <c r="B14" t="n">
         <v>82575</v>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777970</v>
+        <v>778008</v>
       </c>
       <c r="R14" t="n">
-        <v>7299864</v>
+        <v>7299929</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123421319</v>
+        <v>123421323</v>
       </c>
       <c r="B16" t="n">
-        <v>57507</v>
+        <v>82575</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777992</v>
+        <v>778048</v>
       </c>
       <c r="R16" t="n">
-        <v>7299708</v>
+        <v>7299925</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123421320</v>
+        <v>123421322</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>778005</v>
+        <v>778035</v>
       </c>
       <c r="R17" t="n">
-        <v>7299869</v>
+        <v>7299897</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123421323</v>
+        <v>123421320</v>
       </c>
       <c r="B18" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>778048</v>
+        <v>778005</v>
       </c>
       <c r="R18" t="n">
-        <v>7299925</v>
+        <v>7299869</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123421322</v>
+        <v>123421319</v>
       </c>
       <c r="B19" t="n">
-        <v>82575</v>
+        <v>57507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>778035</v>
+        <v>777992</v>
       </c>
       <c r="R19" t="n">
-        <v>7299897</v>
+        <v>7299708</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1900,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123338980</v>
+        <v>123338983</v>
       </c>
       <c r="B14" t="n">
-        <v>82575</v>
+        <v>57411</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,34 +1916,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>102110</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>778008</v>
+        <v>777999</v>
       </c>
       <c r="R14" t="n">
-        <v>7299929</v>
+        <v>7299812</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,17 +2003,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123338983</v>
+        <v>123338980</v>
       </c>
       <c r="B15" t="n">
-        <v>57411</v>
+        <v>82575</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,42 +2026,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102110</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777999</v>
+        <v>778008</v>
       </c>
       <c r="R15" t="n">
-        <v>7299812</v>
+        <v>7299929</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123421322</v>
+        <v>123421319</v>
       </c>
       <c r="B17" t="n">
-        <v>82575</v>
+        <v>57507</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>778035</v>
+        <v>777992</v>
       </c>
       <c r="R17" t="n">
-        <v>7299897</v>
+        <v>7299708</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123421319</v>
+        <v>123421322</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
+        <v>82575</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777992</v>
+        <v>778035</v>
       </c>
       <c r="R19" t="n">
-        <v>7299708</v>
+        <v>7299897</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1900,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123338983</v>
+        <v>123338980</v>
       </c>
       <c r="B14" t="n">
-        <v>57411</v>
+        <v>82575</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,42 +1916,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102110</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777999</v>
+        <v>778008</v>
       </c>
       <c r="R14" t="n">
-        <v>7299812</v>
+        <v>7299929</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,17 +1995,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123338980</v>
+        <v>123338983</v>
       </c>
       <c r="B15" t="n">
-        <v>82575</v>
+        <v>57411</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,34 +2018,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>102110</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>778008</v>
+        <v>777999</v>
       </c>
       <c r="R15" t="n">
-        <v>7299929</v>
+        <v>7299812</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,14 +2105,14 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123421323</v>
+        <v>123421322</v>
       </c>
       <c r="B16" t="n">
         <v>82575</v>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>778048</v>
+        <v>778035</v>
       </c>
       <c r="R16" t="n">
-        <v>7299925</v>
+        <v>7299897</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123421319</v>
+        <v>123421320</v>
       </c>
       <c r="B17" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777992</v>
+        <v>778005</v>
       </c>
       <c r="R17" t="n">
-        <v>7299708</v>
+        <v>7299869</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123421320</v>
+        <v>123421319</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>778005</v>
+        <v>777992</v>
       </c>
       <c r="R18" t="n">
-        <v>7299869</v>
+        <v>7299708</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123421322</v>
+        <v>123421323</v>
       </c>
       <c r="B19" t="n">
         <v>82575</v>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>778035</v>
+        <v>778048</v>
       </c>
       <c r="R19" t="n">
-        <v>7299897</v>
+        <v>7299925</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1798,7 +1798,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123338979</v>
+        <v>123338980</v>
       </c>
       <c r="B13" t="n">
         <v>82575</v>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777970</v>
+        <v>778008</v>
       </c>
       <c r="R13" t="n">
-        <v>7299864</v>
+        <v>7299929</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123338980</v>
+        <v>123338983</v>
       </c>
       <c r="B14" t="n">
-        <v>82575</v>
+        <v>57411</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,34 +1916,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>102110</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>778008</v>
+        <v>777999</v>
       </c>
       <c r="R14" t="n">
-        <v>7299929</v>
+        <v>7299812</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,17 +2003,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123338983</v>
+        <v>123338979</v>
       </c>
       <c r="B15" t="n">
-        <v>57411</v>
+        <v>82575</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,42 +2026,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102110</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777999</v>
+        <v>777970</v>
       </c>
       <c r="R15" t="n">
-        <v>7299812</v>
+        <v>7299864</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,17 +2105,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123421322</v>
+        <v>123421319</v>
       </c>
       <c r="B16" t="n">
-        <v>82575</v>
+        <v>57507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>778035</v>
+        <v>777992</v>
       </c>
       <c r="R16" t="n">
-        <v>7299897</v>
+        <v>7299708</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123421320</v>
+        <v>123421322</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>778005</v>
+        <v>778035</v>
       </c>
       <c r="R17" t="n">
-        <v>7299869</v>
+        <v>7299897</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123421319</v>
+        <v>123421323</v>
       </c>
       <c r="B18" t="n">
-        <v>57507</v>
+        <v>82575</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777992</v>
+        <v>778048</v>
       </c>
       <c r="R18" t="n">
-        <v>7299708</v>
+        <v>7299925</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123421323</v>
+        <v>123421320</v>
       </c>
       <c r="B19" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>778048</v>
+        <v>778005</v>
       </c>
       <c r="R19" t="n">
-        <v>7299925</v>
+        <v>7299869</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123421319</v>
+        <v>123421320</v>
       </c>
       <c r="B16" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777992</v>
+        <v>778005</v>
       </c>
       <c r="R16" t="n">
-        <v>7299708</v>
+        <v>7299869</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123421323</v>
+        <v>123421319</v>
       </c>
       <c r="B18" t="n">
-        <v>82575</v>
+        <v>57507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>778048</v>
+        <v>777992</v>
       </c>
       <c r="R18" t="n">
-        <v>7299925</v>
+        <v>7299708</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123421320</v>
+        <v>123421323</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>778005</v>
+        <v>778048</v>
       </c>
       <c r="R19" t="n">
-        <v>7299869</v>
+        <v>7299925</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2518,6 +2518,200 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128120074</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91448</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>777960</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7299819</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128120069</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58055</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>778034</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7299780</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -2523,7 +2523,7 @@
         <v>128120074</v>
       </c>
       <c r="B20" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>128120069</v>
       </c>
       <c r="B21" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -2523,7 +2523,7 @@
         <v>128120074</v>
       </c>
       <c r="B20" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -2523,7 +2523,7 @@
         <v>128120074</v>
       </c>
       <c r="B20" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1903,12 +1903,7 @@
         <v>123338983</v>
       </c>
       <c r="B14" t="n">
-        <v>57411</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57834</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1903,7 +1903,7 @@
         <v>123338983</v>
       </c>
       <c r="B14" t="n">
-        <v>57834</v>
+        <v>57836</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1903,7 +1903,7 @@
         <v>123338983</v>
       </c>
       <c r="B14" t="n">
-        <v>57836</v>
+        <v>57837</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1903,7 +1903,7 @@
         <v>123338983</v>
       </c>
       <c r="B14" t="n">
-        <v>57837</v>
+        <v>57838</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1903,7 +1903,7 @@
         <v>123338983</v>
       </c>
       <c r="B14" t="n">
-        <v>57838</v>
+        <v>57841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -1903,7 +1903,7 @@
         <v>123338983</v>
       </c>
       <c r="B14" t="n">
-        <v>57841</v>
+        <v>57842</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120276078</v>
+        <v>120447938</v>
       </c>
       <c r="B2" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>778023</v>
+        <v>777894</v>
       </c>
       <c r="R2" t="n">
-        <v>7299762</v>
+        <v>7299834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120276067</v>
+        <v>128120074</v>
       </c>
       <c r="B3" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +808,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778026</v>
+        <v>777960</v>
       </c>
       <c r="R3" t="n">
-        <v>7299789</v>
+        <v>7299819</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +838,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,37 +870,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120276082</v>
+        <v>120447944</v>
       </c>
       <c r="B4" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778126</v>
+        <v>777914</v>
       </c>
       <c r="R4" t="n">
-        <v>7299758</v>
+        <v>7299812</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +935,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,37 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120276077</v>
+        <v>123338979</v>
       </c>
       <c r="B5" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778024</v>
+        <v>777970</v>
       </c>
       <c r="R5" t="n">
-        <v>7299781</v>
+        <v>7299864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1032,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,49 +1052,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120276081</v>
+        <v>123338980</v>
       </c>
       <c r="B6" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778112</v>
+        <v>778008</v>
       </c>
       <c r="R6" t="n">
-        <v>7299748</v>
+        <v>7299929</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1129,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,27 +1149,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120447938</v>
+        <v>123421322</v>
       </c>
       <c r="B7" t="n">
-        <v>78672</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1172,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777894</v>
+        <v>778035</v>
       </c>
       <c r="R7" t="n">
-        <v>7299834</v>
+        <v>7299897</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1226,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1269,7 +1240,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1288,15 +1258,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120447910</v>
+        <v>123421323</v>
       </c>
       <c r="B8" t="n">
-        <v>74698</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1304,21 +1269,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1328,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777954</v>
+        <v>778048</v>
       </c>
       <c r="R8" t="n">
-        <v>7299815</v>
+        <v>7299925</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,12 +1323,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1390,15 +1355,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120447944</v>
+        <v>128120075</v>
       </c>
       <c r="B9" t="n">
-        <v>82374</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,13 +1390,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777914</v>
+        <v>777878</v>
       </c>
       <c r="R9" t="n">
-        <v>7299812</v>
+        <v>7299773</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1460,12 +1420,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1492,37 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120447939</v>
+        <v>122857762</v>
       </c>
       <c r="B10" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1532,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777918</v>
+        <v>778016</v>
       </c>
       <c r="R10" t="n">
-        <v>7299801</v>
+        <v>7299730</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,12 +1517,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1582,27 +1537,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122857765</v>
+        <v>120447939</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1610,21 +1560,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>778128</v>
+        <v>777918</v>
       </c>
       <c r="R11" t="n">
-        <v>7299758</v>
+        <v>7299801</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1664,12 +1614,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1684,49 +1634,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122857762</v>
+        <v>123421320</v>
       </c>
       <c r="B12" t="n">
-        <v>94404</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>778016</v>
+        <v>778005</v>
       </c>
       <c r="R12" t="n">
-        <v>7299730</v>
+        <v>7299869</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,12 +1711,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,27 +1731,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123338980</v>
+        <v>120447910</v>
       </c>
       <c r="B13" t="n">
-        <v>82575</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1814,21 +1754,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1838,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>778008</v>
+        <v>777954</v>
       </c>
       <c r="R13" t="n">
-        <v>7299929</v>
+        <v>7299815</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1868,12 +1808,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1888,65 +1828,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123338983</v>
+        <v>120276067</v>
       </c>
       <c r="B14" t="n">
-        <v>57854</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102110</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777999</v>
+        <v>778026</v>
       </c>
       <c r="R14" t="n">
-        <v>7299812</v>
+        <v>7299789</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,12 +1905,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1993,49 +1925,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123338979</v>
+        <v>122857761</v>
       </c>
       <c r="B15" t="n">
-        <v>82575</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +1972,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777970</v>
+        <v>778064</v>
       </c>
       <c r="R15" t="n">
-        <v>7299864</v>
+        <v>7299707</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2075,12 +2002,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2107,37 +2034,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123421322</v>
+        <v>123421319</v>
       </c>
       <c r="B16" t="n">
-        <v>82597</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2147,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>778035</v>
+        <v>777992</v>
       </c>
       <c r="R16" t="n">
-        <v>7299897</v>
+        <v>7299708</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,37 +2131,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123421319</v>
+        <v>123421318</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2249,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777992</v>
+        <v>778065</v>
       </c>
       <c r="R17" t="n">
-        <v>7299708</v>
+        <v>7299950</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,50 +2228,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123421320</v>
+        <v>123338983</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57903</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>102110</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kallkilmyran, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>778005</v>
+        <v>777999</v>
       </c>
       <c r="R18" t="n">
-        <v>7299869</v>
+        <v>7299812</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2401,49 +2321,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123421323</v>
+        <v>128120069</v>
       </c>
       <c r="B19" t="n">
-        <v>82597</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2453,13 +2368,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>778048</v>
+        <v>778034</v>
       </c>
       <c r="R19" t="n">
-        <v>7299925</v>
+        <v>7299780</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2483,12 +2398,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2515,32 +2430,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128120074</v>
+        <v>120276077</v>
       </c>
       <c r="B20" t="n">
-        <v>91463</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2550,13 +2465,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777960</v>
+        <v>778024</v>
       </c>
       <c r="R20" t="n">
-        <v>7299819</v>
+        <v>7299781</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2580,12 +2495,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2612,32 +2527,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128120069</v>
+        <v>120276078</v>
       </c>
       <c r="B21" t="n">
-        <v>58059</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2647,13 +2562,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>778034</v>
+        <v>778023</v>
       </c>
       <c r="R21" t="n">
-        <v>7299780</v>
+        <v>7299762</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2677,12 +2592,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2706,6 +2621,491 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120276080</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>778099</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7299717</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120276081</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>778112</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7299748</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120276082</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>778126</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7299758</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120276084</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>778142</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7299749</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122857765</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kallkilmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>778128</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7299758</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40107-2024 artfynd.xlsx
+++ b/artfynd/A 40107-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120447938</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120074</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120447944</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123338979</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123338980</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123421322</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123421323</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120075</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122857762</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120447939</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123421320</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120447910</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1934,6 +1999,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120276067</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2031,6 +2101,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122857761</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2128,6 +2203,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123421319</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2225,6 +2305,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123421318</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2330,6 +2415,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123338983</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2427,6 +2517,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128120069</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2524,6 +2619,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120276077</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2621,6 +2721,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120276078</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2718,6 +2823,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120276080</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2815,6 +2925,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120276081</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2912,6 +3027,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120276082</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3009,6 +3129,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120276084</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3106,8 +3231,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122857765</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>